--- a/artfynd/A 21499-2022 artfynd.xlsx
+++ b/artfynd/A 21499-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21499-2022 artfynd.xlsx
+++ b/artfynd/A 21499-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>16628810</v>
       </c>
       <c r="B2" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,14 +695,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>25</t>
@@ -725,13 +716,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>506651.3558780345</v>
+        <v>506651</v>
       </c>
       <c r="R2" t="n">
-        <v>6684169.200483122</v>
+        <v>6684169</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,19 +749,9 @@
           <t>2014-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
